--- a/data/languages/ru.xlsx
+++ b/data/languages/ru.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -148,6 +148,45 @@
     <t xml:space="preserve">Громкость Музики</t>
   </si>
   <si>
+    <t xml:space="preserve">download_music_dlc_btn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скачать доп. музыкальное DLC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">redownload_music_dlc_btn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перекачать доп. музыкальное DLC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">remove_music_dlc_btn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удалить доп. музыкальное DLC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">download_music_dlc_description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Загружает дополнотельное музыкальное DLC с Google Drive
+Требуется 51 МБ свободного места на диске
+ПРИМЕЧАНИЕ:
+Если загрузка с сервера будет слишком интенсивной, она может не работать. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">remove_music_dlc_description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удаляет дополнительную музику DLC,\n но ты потеряешь дополнительную музыку. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Язик</t>
+  </si>
+  <si>
     <t xml:space="preserve">droopers</t>
   </si>
   <si>
@@ -253,7 +292,7 @@
     <t xml:space="preserve">disclaimer_content</t>
   </si>
   <si>
-    <t xml:space="preserve">Этот фанатский проект не поддерживается и не связан с Paradoxum Games,
+    <t xml:space="preserve">Этот фанатский проект не связан с Paradoxum Games,
 и её разработчиками каким-либо образом, а также с Roblox Corporation и другими компаниями. Не продавайте и не распространяйте этот проект
 платно, он всегда будет бесплатным.
 Если вы хотите поддержать меня, подписывайтесь на меня в социальных сетях!
@@ -265,6 +304,18 @@
   </si>
   <si>
     <t xml:space="preserve">Внимание!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disclaimer_indev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эта игра еще в разработке и поэтому игровое\nвремя и контента может бить мало.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disclaimer_dev_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ви играете или тестируете версию з исходного кода, ви можете увидеть баги и не завершенний контент ви били предупреждены.</t>
   </si>
   <si>
     <t xml:space="preserve">not_enough_coins</t>
@@ -360,13 +411,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -500,7 +559,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.53"/>
@@ -676,42 +735,42 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="0" t="s">
         <v>46</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="25" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
     </row>
@@ -743,7 +802,7 @@
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="4" t="s">
         <v>59</v>
       </c>
     </row>
@@ -811,11 +870,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -842,6 +901,74 @@
       <c r="B42" s="1" t="s">
         <v>83</v>
       </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0"/>
+      <c r="B51" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
